--- a/Indore-March-2026.xlsx
+++ b/Indore-March-2026.xlsx
@@ -106,10 +106,10 @@
     <t>MH02FX1146</t>
   </si>
   <si>
-    <t>Crysta</t>
-  </si>
-  <si>
-    <t>Dzire CNG</t>
+    <t>CRYSTA</t>
+  </si>
+  <si>
+    <t>DZIRE</t>
   </si>
   <si>
     <t>21/09/2021</t>
